--- a/database/schedule_sample.xlsx
+++ b/database/schedule_sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Job\SMAN 5 Garut\2025-2026\Kurikulum\PSAS\Jadwal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Indie life project\exam app\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB6DDF61-5E4E-4E2A-A242-167BEF890750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88364811-339A-48CC-8231-1C43AEC465E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31EF4A0F-8F46-4422-B733-4D77F14B6608}"/>
   </bookViews>
@@ -458,18 +458,12 @@
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -529,9 +523,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -549,6 +540,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,13 +908,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -937,6 +930,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1350,13 +1350,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1366,6 +1359,13 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1385,7 +1385,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A6360DAF-A8F2-4A9A-8206-B5D90F42CCEB}" name="Table1" displayName="Table1" ref="B20:Q32" totalsRowShown="0" headerRowBorderDxfId="36" tableBorderDxfId="37" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A6360DAF-A8F2-4A9A-8206-B5D90F42CCEB}" name="Table1" displayName="Table1" ref="B20:Q32" totalsRowShown="0" headerRowBorderDxfId="37" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="B20:Q32" xr:uid="{A6360DAF-A8F2-4A9A-8206-B5D90F42CCEB}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{D98BF157-FF35-4648-A308-9E87C1178BDA}" name="Column1" dataDxfId="34"/>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{341EBAB3-DD3A-4D8C-8DA9-C28F9692C81B}" name="Table3" displayName="Table3" ref="B3:O15" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{341EBAB3-DD3A-4D8C-8DA9-C28F9692C81B}" name="Table3" displayName="Table3" ref="B3:O15" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="B3:O15" xr:uid="{341EBAB3-DD3A-4D8C-8DA9-C28F9692C81B}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{7FAECD10-B7B5-4431-9678-35091DEBA362}" name="Column1" dataDxfId="13"/>
@@ -1733,1498 +1733,1498 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="23" t="s">
+      <c r="O6" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O8" s="23" t="s">
+      <c r="O8" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="23" t="s">
+      <c r="O9" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="23" t="s">
+      <c r="O10" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="23" t="s">
+      <c r="O11" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="23" t="s">
+      <c r="O12" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="O13" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="O14" s="23" t="s">
+      <c r="O14" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="29" t="s">
+      <c r="L15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M15" s="29" t="s">
+      <c r="M15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="N15" s="30" t="s">
+      <c r="N15" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="O15" s="31" t="s">
+      <c r="O15" s="29" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="L18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="6" t="s">
+      <c r="O18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="P18" s="7" t="s">
+      <c r="P18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q18" s="7" t="s">
+      <c r="Q18" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="N19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="O19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="P19" s="33" t="s">
+      <c r="P19" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q19" s="33" t="s">
+      <c r="Q19" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="37" t="s">
+      <c r="N20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="O20" s="37" t="s">
+      <c r="O20" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="P20" s="38" t="s">
+      <c r="P20" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="Q20" s="39" t="s">
+      <c r="Q20" s="36" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O21" s="6" t="s">
+      <c r="O21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P21" s="7" t="s">
+      <c r="P21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q21" s="41" t="s">
+      <c r="Q21" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="L22" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="M22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O22" s="6" t="s">
+      <c r="O22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P22" s="7" t="s">
+      <c r="P22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q22" s="41" t="s">
+      <c r="Q22" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="L23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="M23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O23" s="6" t="s">
+      <c r="O23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="7" t="s">
+      <c r="P23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q23" s="41" t="s">
+      <c r="Q23" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K24" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="L24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="O24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P24" s="7" t="s">
+      <c r="P24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q24" s="41" t="s">
+      <c r="Q24" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L25" s="5" t="s">
+      <c r="L25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="M25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="N25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O25" s="6" t="s">
+      <c r="O25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="P25" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q25" s="41" t="s">
+      <c r="Q25" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="L26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="M26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N26" s="6" t="s">
+      <c r="N26" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O26" s="6" t="s">
+      <c r="O26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P26" s="7" t="s">
+      <c r="P26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q26" s="41" t="s">
+      <c r="Q26" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L27" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="M27" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N27" s="6" t="s">
+      <c r="N27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O27" s="6" t="s">
+      <c r="O27" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P27" s="7" t="s">
+      <c r="P27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q27" s="41" t="s">
+      <c r="Q27" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="L28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M28" s="5" t="s">
+      <c r="M28" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O28" s="6" t="s">
+      <c r="O28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P28" s="7" t="s">
+      <c r="P28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q28" s="41" t="s">
+      <c r="Q28" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="L29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="M29" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="N29" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O29" s="6" t="s">
+      <c r="O29" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P29" s="7" t="s">
+      <c r="P29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q29" s="41" t="s">
+      <c r="Q29" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K30" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="L30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M30" s="5" t="s">
+      <c r="M30" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N30" s="6" t="s">
+      <c r="N30" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="O30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="P30" s="7" t="s">
+      <c r="P30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q30" s="41" t="s">
+      <c r="Q30" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="L31" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M31" s="5" t="s">
+      <c r="M31" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="6" t="s">
+      <c r="N31" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O31" s="6" t="s">
+      <c r="O31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="P31" s="7" t="s">
+      <c r="P31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q31" s="41" t="s">
+      <c r="Q31" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
+      <c r="A32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="43" t="s">
+      <c r="C32" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="44" t="s">
+      <c r="F32" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="G32" s="44" t="s">
+      <c r="G32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H32" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J32" s="27" t="s">
+      <c r="J32" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="29" t="s">
+      <c r="K32" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="L32" s="29" t="s">
+      <c r="L32" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M32" s="29" t="s">
+      <c r="M32" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="N32" s="45" t="s">
+      <c r="N32" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="O32" s="45" t="s">
+      <c r="O32" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="P32" s="46" t="s">
+      <c r="P32" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="Q32" s="47" t="s">
+      <c r="Q32" s="44" t="s">
         <v>48</v>
       </c>
     </row>
